--- a/budget_model.xlsx
+++ b/budget_model.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="202">
   <si>
     <r>
       <rPr>
@@ -2250,6 +2250,242 @@
     <t xml:space="preserve">損害賠償責任保険</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自社チャンネル投資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月開始。営業実績づくり </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">市場反応データ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PLATFORM_REVENUE.md)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自社チャンネル投資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">拡大分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月に月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本へ拡大。上記と合わせて月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万になる</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">フル体制での月次固定費</t>
   </si>
   <si>
@@ -2317,6 +2553,55 @@
       </rPr>
       <t xml:space="preserve">平均単価</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">うち 自社チャンネル投資</t>
+  </si>
+  <si>
+    <t xml:space="preserve">営業のための投資。上の損益分岐にはこれも含まれています</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">損益分岐 月間本数</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チャンネル投資を除く</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">チャンネルを止めた場合の損益分岐。撤退判断のときに見る数字</t>
   </si>
   <si>
     <r>
@@ -5191,7 +5476,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -5534,48 +5819,120 @@
       <c r="G17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="24" t="n">
-        <f aca="false">SUM(C5:C17)</f>
-        <v>166</v>
-      </c>
-      <c r="D18" s="24" t="n">
-        <f aca="false">SUM(D5:D17)</f>
-        <v>229</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <f aca="false">SUM(E5:E17)</f>
-        <v>226</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <f aca="false">SUM(F5:F17)</f>
-        <v>226</v>
+      <c r="B18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <f aca="false">INDEX(C18:E18,前提!$B$11)</f>
+        <v>20</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <f aca="false">INDEX(C19:E19,前提!$B$11)</f>
+        <v>25</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <f aca="false">F18/前提!$E$34</f>
-        <v>417.230769230769</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="26" t="n">
-        <f aca="false">F20/前提!$B$21</f>
+        <v>108</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <f aca="false">SUM(C5:C19)</f>
+        <v>211</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <f aca="false">SUM(D5:D19)</f>
+        <v>274</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <f aca="false">SUM(E5:E19)</f>
+        <v>271</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <f aca="false">SUM(F5:F19)</f>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <f aca="false">F20/前提!$E$34</f>
+        <v>500.307692307692</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="26" t="n">
+        <f aca="false">F22/前提!$B$21</f>
+        <v>10.4230769230769</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <f aca="false">SUM(F18:F19)</f>
+        <v>45</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <f aca="false">(F20-F25)/前提!$E$34/前提!$B$21</f>
         <v>8.69230769230769</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>108</v>
+      <c r="G26" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -5604,17 +5961,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B4" s="27" t="n">
         <v>1</v>
@@ -5655,48 +6012,48 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>0</v>
@@ -5735,12 +6092,12 @@
         <v>5</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B7" s="29" t="n">
         <f aca="false">B6*前提!$B$21</f>
@@ -5793,7 +6150,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B9" s="29" t="n">
         <v>0</v>
@@ -5845,7 +6202,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">前提!$B$14</f>
@@ -5887,7 +6244,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">IF(B4=前提!$B$16,前提!$B$15,0)</f>
@@ -5940,7 +6297,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM(B9:B11)</f>
@@ -5993,7 +6350,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">SUMIF(初期費用!$B$5:$B$17,B4,初期費用!$F$5:$F$17)</f>
@@ -6046,60 +6403,60 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;B4,月次固定費!$F$5:$F$17)</f>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;B4,月次固定費!$F$5:$F$19)</f>
         <v>56</v>
       </c>
       <c r="C15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;C4,月次固定費!$F$5:$F$17)</f>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;C4,月次固定費!$F$5:$F$19)</f>
         <v>56</v>
       </c>
       <c r="D15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;D4,月次固定費!$F$5:$F$17)</f>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;D4,月次固定費!$F$5:$F$19)</f>
         <v>106</v>
       </c>
       <c r="E15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;E4,月次固定費!$F$5:$F$17)</f>
-        <v>166</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;E4,月次固定費!$F$5:$F$19)</f>
+        <v>186</v>
       </c>
       <c r="F15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;F4,月次固定費!$F$5:$F$17)</f>
-        <v>166</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;F4,月次固定費!$F$5:$F$19)</f>
+        <v>186</v>
       </c>
       <c r="G15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;G4,月次固定費!$F$5:$F$17)</f>
-        <v>166</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;G4,月次固定費!$F$5:$F$19)</f>
+        <v>186</v>
       </c>
       <c r="H15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;H4,月次固定費!$F$5:$F$17)</f>
-        <v>226</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;H4,月次固定費!$F$5:$F$19)</f>
+        <v>271</v>
       </c>
       <c r="I15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;I4,月次固定費!$F$5:$F$17)</f>
-        <v>226</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;I4,月次固定費!$F$5:$F$19)</f>
+        <v>271</v>
       </c>
       <c r="J15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;J4,月次固定費!$F$5:$F$17)</f>
-        <v>226</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;J4,月次固定費!$F$5:$F$19)</f>
+        <v>271</v>
       </c>
       <c r="K15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;K4,月次固定費!$F$5:$F$17)</f>
-        <v>226</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;K4,月次固定費!$F$5:$F$19)</f>
+        <v>271</v>
       </c>
       <c r="L15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;L4,月次固定費!$F$5:$F$17)</f>
-        <v>226</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;L4,月次固定費!$F$5:$F$19)</f>
+        <v>271</v>
       </c>
       <c r="M15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$17,"&lt;="&amp;M4,月次固定費!$F$5:$F$17)</f>
-        <v>226</v>
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;M4,月次固定費!$F$5:$F$19)</f>
+        <v>271</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">B6*前提!$E$33</f>
@@ -6152,7 +6509,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">IF(B4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
@@ -6205,7 +6562,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B18" s="23" t="n">
         <f aca="false">SUM(B14:B17)</f>
@@ -6221,44 +6578,44 @@
       </c>
       <c r="E18" s="23" t="n">
         <f aca="false">SUM(E14:E17)</f>
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="F18" s="23" t="n">
         <f aca="false">SUM(F14:F17)</f>
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="G18" s="23" t="n">
         <f aca="false">SUM(G14:G17)</f>
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="H18" s="23" t="n">
         <f aca="false">SUM(H14:H17)</f>
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="I18" s="23" t="n">
         <f aca="false">SUM(I14:I17)</f>
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="J18" s="23" t="n">
         <f aca="false">SUM(J14:J17)</f>
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="K18" s="23" t="n">
         <f aca="false">SUM(K14:K17)</f>
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="L18" s="23" t="n">
         <f aca="false">SUM(L14:L17)</f>
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="M18" s="23" t="n">
         <f aca="false">SUM(M14:M17)</f>
-        <v>341</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B20" s="23" t="n">
         <f aca="false">B12-B18</f>
@@ -6274,44 +6631,44 @@
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">E12-E18</f>
-        <v>-193</v>
+        <v>-213</v>
       </c>
       <c r="F20" s="23" t="n">
         <f aca="false">F12-F18</f>
-        <v>-167</v>
+        <v>-187</v>
       </c>
       <c r="G20" s="23" t="n">
         <f aca="false">G12-G18</f>
-        <v>-119</v>
+        <v>-139</v>
       </c>
       <c r="H20" s="23" t="n">
         <f aca="false">H12-H18</f>
-        <v>-201</v>
+        <v>-246</v>
       </c>
       <c r="I20" s="23" t="n">
         <f aca="false">I12-I18</f>
-        <v>-153</v>
+        <v>-198</v>
       </c>
       <c r="J20" s="23" t="n">
         <f aca="false">J12-J18</f>
-        <v>-175</v>
+        <v>-220</v>
       </c>
       <c r="K20" s="23" t="n">
         <f aca="false">K12-K18</f>
-        <v>-127</v>
+        <v>-172</v>
       </c>
       <c r="L20" s="23" t="n">
         <f aca="false">L12-L18</f>
-        <v>-149</v>
+        <v>-194</v>
       </c>
       <c r="M20" s="23" t="n">
         <f aca="false">M12-M18</f>
-        <v>-101</v>
+        <v>-146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B21" s="30" t="n">
         <f aca="false">B20</f>
@@ -6327,53 +6684,53 @@
       </c>
       <c r="E21" s="30" t="n">
         <f aca="false">D21+E20</f>
-        <v>1492.35</v>
+        <v>1472.35</v>
       </c>
       <c r="F21" s="30" t="n">
         <f aca="false">E21+F20</f>
-        <v>1325.35</v>
+        <v>1285.35</v>
       </c>
       <c r="G21" s="30" t="n">
         <f aca="false">F21+G20</f>
-        <v>1206.35</v>
+        <v>1146.35</v>
       </c>
       <c r="H21" s="30" t="n">
         <f aca="false">G21+H20</f>
-        <v>1005.35</v>
+        <v>900.35</v>
       </c>
       <c r="I21" s="30" t="n">
         <f aca="false">H21+I20</f>
-        <v>852.35</v>
+        <v>702.35</v>
       </c>
       <c r="J21" s="30" t="n">
         <f aca="false">I21+J20</f>
-        <v>677.35</v>
+        <v>482.35</v>
       </c>
       <c r="K21" s="30" t="n">
         <f aca="false">J21+K20</f>
-        <v>550.35</v>
+        <v>310.35</v>
       </c>
       <c r="L21" s="30" t="n">
         <f aca="false">K21+L20</f>
-        <v>401.35</v>
+        <v>116.35</v>
       </c>
       <c r="M21" s="30" t="n">
         <f aca="false">L21+M20</f>
-        <v>300.35</v>
+        <v>-29.6500000000001</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B23" s="25" t="n">
         <f aca="false">MIN(B21:M21)</f>
-        <v>300.35</v>
+        <v>-29.6500000000001</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B24" s="20" t="str">
         <f aca="false">INDEX(B5:M5,MATCH(B23,B21:M21,0))</f>
@@ -6382,7 +6739,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B25" s="26" t="n">
         <f aca="false">SUM(B6:M6)</f>
@@ -6391,7 +6748,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B26" s="25" t="n">
         <f aca="false">SUM(B7:M7)</f>
@@ -6424,49 +6781,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B4" s="22" t="n">
         <f aca="false">初期費用!F17</f>
         <v>886.65</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B5" s="22" t="n">
-        <f aca="false">月次固定費!F18</f>
-        <v>226</v>
+        <f aca="false">月次固定費!F20</f>
+        <v>271</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B6" s="31" t="n">
-        <f aca="false">月次固定費!F21</f>
-        <v>8.69230769230769</v>
+        <f aca="false">月次固定費!F23</f>
+        <v>10.4230769230769</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">前提!B14+前提!B15</f>
@@ -6476,19 +6833,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">資金繰り!B23</f>
-        <v>300.35</v>
+        <v>-29.6500000000001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B10" s="6" t="str">
         <f aca="false">資金繰り!B24</f>
@@ -6498,73 +6855,73 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">資金繰り!M21</f>
-        <v>300.35</v>
+        <v>-29.6500000000001</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B13" s="22" t="n">
-        <f aca="false">月次固定費!F18*前提!B18</f>
-        <v>678</v>
+        <f aca="false">月次固定費!F20*前提!B18</f>
+        <v>813</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B14" s="25" t="n">
-        <f aca="false">MAX(0,月次固定費!F18*前提!B18-資金繰り!B23)</f>
-        <v>377.65</v>
+        <f aca="false">MAX(0,月次固定費!F20*前提!B18-資金繰り!B23)</f>
+        <v>842.65</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">B8+B14</f>
-        <v>3177.65</v>
+        <v>3642.65</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6572,12 +6929,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -6605,34 +6962,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="33" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>35</v>
@@ -6652,7 +7009,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>48</v>
@@ -6672,7 +7029,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>22</v>
@@ -6692,7 +7049,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>0</v>
@@ -6712,7 +7069,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>0.2</v>
@@ -6732,7 +7089,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>3</v>
@@ -6752,7 +7109,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>720</v>
@@ -6772,7 +7129,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>0.6</v>
@@ -6792,7 +7149,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1100</v>
@@ -6812,7 +7169,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B15" s="29" t="n">
         <f aca="false">B5*B6</f>
@@ -6837,7 +7194,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B16" s="29" t="n">
         <f aca="false">B8</f>
@@ -6862,7 +7219,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">B15+B16</f>
@@ -6887,7 +7244,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">B5*B7+B8*B9</f>
@@ -6912,7 +7269,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B19" s="23" t="n">
         <f aca="false">B17-B18</f>
@@ -6962,7 +7319,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">B10*B11*B12</f>
@@ -6987,7 +7344,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B22" s="29" t="n">
         <f aca="false">B13</f>
@@ -7012,7 +7369,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">B21+B22</f>
@@ -7037,7 +7394,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B24" s="24" t="n">
         <f aca="false">B19-B23</f>
@@ -7062,7 +7419,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B25" s="34" t="n">
         <f aca="false">IF(B17=0,0,B24/B17)</f>
@@ -7087,7 +7444,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B27" s="35" t="n">
         <f aca="false">IF(B17=0,0,B16/B17)</f>
@@ -7112,7 +7469,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B28" s="29" t="n">
         <f aca="false">IF(B10=0,0,B17/B10)</f>
@@ -7137,17 +7494,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/budget_model.xlsx
+++ b/budget_model.xlsx
@@ -11,9 +11,10 @@
     <sheet name="前提" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="初期費用" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="月次固定費" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="資金繰り" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="必要調達" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="年次PL" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="販売費・チャネル" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="資金繰り" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="必要調達" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="年次PL" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="254">
   <si>
     <r>
       <rPr>
@@ -2211,7 +2212,190 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">営業活動費</t>
+    <t xml:space="preserve">営業交通費・会議費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商談の移動・会食。出稿費とは分ける</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リード獲得費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リスト・ツール・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IS)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商談の実体。ここが空欄だと売上計画の根拠が消える</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告宣伝費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出稿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目は絞る。事例が出るまで効かない。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目から月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">送金手数料</t>
@@ -2602,6 +2786,143 @@
   </si>
   <si>
     <t xml:space="preserve">チャンネルを止めた場合の損益分岐。撤退判断のときに見る数字</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">うち 販売費</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交通・リード獲得・広告</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次受け主軸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の水準。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案は月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">68</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万 →『販売費・チャネル』シート</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2612,7 +2933,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C. </t>
+      <t xml:space="preserve">E. </t>
     </r>
     <r>
       <rPr>
@@ -2621,7 +2942,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月次資金繰り</t>
+      <t xml:space="preserve">販売費とチャネル戦略 — </t>
     </r>
     <r>
       <rPr>
@@ -2631,7 +2952,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(1</t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -2640,7 +2961,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年目</t>
+      <t xml:space="preserve">案 </t>
     </r>
     <r>
       <rPr>
@@ -2650,999 +2971,2041 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">単位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">受注本数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を書き換えると全体が動きます</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">受注・納品本数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">← 青字・黄色。ここが最上位のドライバー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売上高</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">入金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">売上・翌月末</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">資本金の払込</t>
-  </si>
-  <si>
-    <t xml:space="preserve">融資の着金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入金 合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">初期費用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次固定費</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">変動費</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">制作原価</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">支払利息</t>
-  </si>
-  <si>
-    <t xml:space="preserve">支出 合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次収支</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月末残高</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最低残高</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最低残高の月</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目の受注 合計</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目の売上 合計</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">/ B</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D. </t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案の比較</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本数は月あたり。すべて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仮置き</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。青字が入力、黒字が計算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チャネル別の単価・原価・営業生産性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">直販</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自社で受注</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次受け</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代理店の下請</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">平均単価</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次受けは代理店の制作予算圧縮ニーズ。直販の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">割強</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本あたり原価</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次受けは企画・要件定義が代理店側。中国側支払が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13→8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本あたり粗利</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の月間受注本数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次受けは代理店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社との反復受注。商談は月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件で足りる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チャネルミックスと販売費</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次受け主軸</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">直販主軸</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次受けの比率</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最重要の前提。ここが戦略そのもの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">直販の比率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平均単価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加重</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本あたり原価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加重</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の月間受注本数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加重</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案は新規直販なのでインサイドセールスの規模が要る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目から張らないと商談が積み上がらない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">販売費 合計</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">黒字化に必要な体制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">制作ディレクター</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の月間処理本数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">160</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の月額人件費</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ディレクター</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の月額人件費</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共通固定費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">販売費・営業・ディレクターを除く</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">役員報酬・オフィス・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SaaS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・自社チャンネル等</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名あたりの純貢献</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">粗利 − 自分の人件費 − 必要なディレクターの人件費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黒字化に必要な営業人数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黒字化に必要なディレクター人数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">律速になる職種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人数が多い側が律速。採用しやすい側が律速である方が望ましい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そのときの月間本数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そのときの月商</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日本側の総人数</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代表含む</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中国側クリエイター</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稼働・月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">登録プールはこの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(CHINA_SOURCING.md 4-3)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">読み方</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・どちらの案でも、日本側</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名にならないと単月黒字化しません。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は構造的に赤字です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案は律速が制作ディレクター、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案は律速が営業。ディレクターの方が採用も立ち上がりも早いので</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案を推奨します。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案は販売費が月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">48</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万少ないぶん、黒字化まで現金の減り方が緩やかです。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・このシートは体制の逆算専用です。全体を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案で回すには『前提』</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B21(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平均単価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と変動費を</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  このシートの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案の加重値に置き換えてください</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資金繰り・年次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が連動します</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">必要調達額</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">単位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">初期費用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">予備費込み</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">選択シナリオ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フル体制の月次固定費</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在の調達額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">資本金 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">融資</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目の最低残高</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">マイナスなら資金が尽きる</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目末の残高</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標バッファ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">固定費 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目末に残したい額</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">追加で必要な調達</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最低残高を目標バッファまで引き上げる額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">推奨する調達総額</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在の調達 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">追加</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">読み方</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">『前提』</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">でシナリオを切り替える</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">楽観 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ 2=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">標準 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ 3=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実行可能版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">『資金繰り』</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目の受注本数を、自分の見込みに書き換える</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">『必要調達』の「推奨する調達総額」を見る。ここが今の調達額を超えていれば足りない</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最低残高がマイナスなら、その月に資金が尽きる。採用の開始月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">『月次固定費』</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を後ろに倒して調整する</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ このモデルは</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目のみ。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目以降は『年次</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">』シート。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 消費税</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海外発注は仕入税額控除が取れない可能性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は未反映。税理士の確認後に原価へ上乗せしてください。</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C. </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E. 5</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月次資金繰り</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年の損益計画</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">保守版</t>
-    </r>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受注本数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を書き換えると全体が動きます</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受注・納品本数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← 青字・黄色。ここが最上位のドライバー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上高</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">売上・翌月末</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">資本金の払込</t>
+  </si>
+  <si>
+    <t xml:space="preserve">融資の着金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入金 合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初期費用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次固定費</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">変動費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">制作原価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">支払利息</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支出 合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次収支</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月末残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最低残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最低残高の月</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目の受注 合計</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目の売上 合計</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -3651,6 +5014,707 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">D. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">必要調達額</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初期費用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">予備費込み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">選択シナリオ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フル体制の月次固定費</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在の調達額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資本金 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">融資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目の最低残高</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">マイナスなら資金が尽きる</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目末の残高</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標バッファ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固定費 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目末に残したい額</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">追加で必要な調達</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最低残高を目標バッファまで引き上げる額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">推奨する調達総額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在の調達 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">追加</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">『前提』</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でシナリオを切り替える</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">楽観 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 2=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">標準 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 3=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実行可能版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">『資金繰り』</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行目の受注本数を、自分の見込みに書き換える</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">『必要調達』の「推奨する調達総額」を見る。ここが今の調達額を超えていれば足りない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">最低残高がマイナスなら、その月に資金が尽きる。採用の開始月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">『月次固定費』</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を後ろに倒して調整する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ このモデルは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目のみ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目以降は『年次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">』シート。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海外発注は仕入税額控除が取れない可能性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は未反映。税理士の確認後に原価へ上乗せしてください。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E. 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年の損益計画</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保守版</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
@@ -3821,28 +5885,6 @@
   </si>
   <si>
     <t xml:space="preserve">受注本数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平均単価</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本あたり原価</t>
-    </r>
   </si>
   <si>
     <r>
@@ -4343,7 +6385,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4449,6 +6491,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5476,7 +7546,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -5758,47 +7828,49 @@
         <v>1</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F15" s="22" t="n">
         <f aca="false">INDEX(C15:E15,前提!$B$11)</f>
-        <v>15</v>
-      </c>
-      <c r="G15" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16" s="22" t="n">
         <f aca="false">INDEX(C16:E16,前提!$B$11)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>1</v>
@@ -5807,132 +7879,192 @@
         <v>1</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" s="22" t="n">
         <f aca="false">INDEX(C17:E17,前提!$B$11)</f>
-        <v>2</v>
-      </c>
-      <c r="G17" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F18" s="22" t="n">
         <f aca="false">INDEX(C18:E18,前提!$B$11)</f>
-        <v>20</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>105</v>
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F19" s="22" t="n">
         <f aca="false">INDEX(C19:E19,前提!$B$11)</f>
+        <v>2</v>
+      </c>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <f aca="false">INDEX(C20:E20,前提!$B$11)</f>
+        <v>20</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="24" t="n">
-        <f aca="false">SUM(C5:C19)</f>
-        <v>211</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <f aca="false">SUM(D5:D19)</f>
-        <v>274</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <f aca="false">SUM(E5:E19)</f>
-        <v>271</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <f aca="false">SUM(F5:F19)</f>
-        <v>271</v>
+      <c r="D21" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="22" t="n">
+        <f aca="false">INDEX(C21:E21,前提!$B$11)</f>
+        <v>25</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="25" t="n">
-        <f aca="false">F20/前提!$E$34</f>
-        <v>500.307692307692</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="26" t="n">
-        <f aca="false">F22/前提!$B$21</f>
-        <v>10.4230769230769</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <f aca="false">SUM(C5:C21)</f>
+        <v>211</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <f aca="false">SUM(D5:D21)</f>
+        <v>289</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <f aca="false">SUM(E5:E21)</f>
+        <v>276</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <f aca="false">SUM(F5:F21)</f>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <f aca="false">F22/前提!$E$34</f>
+        <v>509.538461538462</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="25" t="n">
-        <f aca="false">SUM(F18:F19)</f>
+        <v>116</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <f aca="false">F24/前提!$B$21</f>
+        <v>10.6153846153846</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="25" t="n">
+        <f aca="false">SUM(F20:F21)</f>
         <v>45</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="26" t="n">
-        <f aca="false">(F20-F25)/前提!$E$34/前提!$B$21</f>
-        <v>8.69230769230769</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>116</v>
+      <c r="G27" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <f aca="false">(F22-F27)/前提!$E$34/前提!$B$21</f>
+        <v>8.88461538461538</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="25" t="n">
+        <f aca="false">SUM(F15:F17)</f>
+        <v>20</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -5951,808 +8083,462 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="I4" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="M4" s="27" t="n">
-        <v>12</v>
+      <c r="A4" s="27" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="H5" s="27" t="s">
+      <c r="A5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="C5" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="D5" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="B6" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="L5" s="27" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="B7" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="29" t="n">
-        <f aca="false">B6*前提!$B$21</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="29" t="n">
-        <f aca="false">C6*前提!$B$21</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <f aca="false">D6*前提!$B$21</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <f aca="false">E6*前提!$B$21</f>
-        <v>48</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <f aca="false">F6*前提!$B$21</f>
-        <v>96</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <f aca="false">G6*前提!$B$21</f>
-        <v>96</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <f aca="false">H6*前提!$B$21</f>
-        <v>144</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <f aca="false">I6*前提!$B$21</f>
-        <v>144</v>
-      </c>
-      <c r="J7" s="29" t="n">
-        <f aca="false">J6*前提!$B$21</f>
-        <v>192</v>
-      </c>
-      <c r="K7" s="29" t="n">
-        <f aca="false">K6*前提!$B$21</f>
-        <v>192</v>
-      </c>
-      <c r="L7" s="29" t="n">
-        <f aca="false">L6*前提!$B$21</f>
-        <v>240</v>
-      </c>
-      <c r="M7" s="29" t="n">
-        <f aca="false">M6*前提!$B$21</f>
-        <v>240</v>
+      <c r="B8" s="19" t="n">
+        <f aca="false">B6-B7</f>
+        <v>26</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">C6-C7</f>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="B9" s="29" t="n">
-        <v>0</v>
+        <f aca="false">B8/B6</f>
+        <v>0.541666666666667</v>
       </c>
       <c r="C9" s="29" t="n">
-        <f aca="false">B7</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <f aca="false">C7</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <f aca="false">D7</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <f aca="false">E7</f>
-        <v>48</v>
-      </c>
-      <c r="G9" s="29" t="n">
-        <f aca="false">F7</f>
-        <v>96</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <f aca="false">G7</f>
-        <v>96</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <f aca="false">H7</f>
-        <v>144</v>
-      </c>
-      <c r="J9" s="29" t="n">
-        <f aca="false">I7</f>
-        <v>144</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <f aca="false">J7</f>
-        <v>192</v>
-      </c>
-      <c r="L9" s="29" t="n">
-        <f aca="false">K7</f>
-        <v>192</v>
-      </c>
-      <c r="M9" s="29" t="n">
-        <f aca="false">L7</f>
-        <v>240</v>
+        <f aca="false">C8/C6</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="22" t="n">
-        <f aca="false">前提!$B$14</f>
-        <v>800</v>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="C13" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="22" t="n">
-        <f aca="false">IF(B4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <f aca="false">IF(C4=前提!$B$16,前提!$B$15,0)</f>
-        <v>2000</v>
-      </c>
-      <c r="D11" s="22" t="n">
-        <f aca="false">IF(D4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <f aca="false">IF(E4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <f aca="false">IF(F4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <f aca="false">IF(G4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <f aca="false">IF(H4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <f aca="false">IF(I4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="22" t="n">
-        <f aca="false">IF(J4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <f aca="false">IF(K4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="22" t="n">
-        <f aca="false">IF(L4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="22" t="n">
-        <f aca="false">IF(M4=前提!$B$16,前提!$B$15,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+      <c r="D13" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="23" t="n">
-        <f aca="false">SUM(B9:B11)</f>
-        <v>800</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <f aca="false">SUM(C9:C11)</f>
-        <v>2000</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <f aca="false">SUM(D9:D11)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <f aca="false">SUM(E9:E11)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <f aca="false">SUM(F9:F11)</f>
-        <v>48</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <f aca="false">SUM(G9:G11)</f>
-        <v>96</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <f aca="false">SUM(H9:H11)</f>
-        <v>96</v>
-      </c>
-      <c r="I12" s="23" t="n">
-        <f aca="false">SUM(I9:I11)</f>
-        <v>144</v>
-      </c>
-      <c r="J12" s="23" t="n">
-        <f aca="false">SUM(J9:J11)</f>
-        <v>144</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <f aca="false">SUM(K9:K11)</f>
-        <v>192</v>
-      </c>
-      <c r="L12" s="23" t="n">
-        <f aca="false">SUM(L9:L11)</f>
-        <v>192</v>
-      </c>
-      <c r="M12" s="23" t="n">
-        <f aca="false">SUM(M9:M11)</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="B14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,B4,初期費用!$F$5:$F$17)</f>
-        <v>131</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,C4,初期費用!$F$5:$F$17)</f>
-        <v>385</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,D4,初期費用!$F$5:$F$17)</f>
-        <v>370.65</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,E4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,F4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,G4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,H4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,I4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,J4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,K4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,L4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="22" t="n">
-        <f aca="false">SUMIF(初期費用!$B$5:$B$17,M4,初期費用!$F$5:$F$17)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;B4,月次固定費!$F$5:$F$19)</f>
-        <v>56</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;C4,月次固定費!$F$5:$F$19)</f>
-        <v>56</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;D4,月次固定費!$F$5:$F$19)</f>
-        <v>106</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;E4,月次固定費!$F$5:$F$19)</f>
-        <v>186</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;F4,月次固定費!$F$5:$F$19)</f>
-        <v>186</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;G4,月次固定費!$F$5:$F$19)</f>
-        <v>186</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;H4,月次固定費!$F$5:$F$19)</f>
-        <v>271</v>
-      </c>
-      <c r="I15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;I4,月次固定費!$F$5:$F$19)</f>
-        <v>271</v>
-      </c>
-      <c r="J15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;J4,月次固定費!$F$5:$F$19)</f>
-        <v>271</v>
-      </c>
-      <c r="K15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;K4,月次固定費!$F$5:$F$19)</f>
-        <v>271</v>
-      </c>
-      <c r="L15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;L4,月次固定費!$F$5:$F$19)</f>
-        <v>271</v>
-      </c>
-      <c r="M15" s="22" t="n">
-        <f aca="false">SUMIF(月次固定費!$B$5:$B$19,"&lt;="&amp;M4,月次固定費!$F$5:$F$19)</f>
-        <v>271</v>
+      <c r="B15" s="29" t="n">
+        <f aca="false">1-B14</f>
+        <v>0.3</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <f aca="false">1-C14</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="22" t="n">
-        <f aca="false">B6*前提!$E$33</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <f aca="false">C6*前提!$E$33</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <f aca="false">D6*前提!$E$33</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <f aca="false">E6*前提!$E$33</f>
-        <v>22</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <f aca="false">F6*前提!$E$33</f>
-        <v>44</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <f aca="false">G6*前提!$E$33</f>
-        <v>44</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <f aca="false">H6*前提!$E$33</f>
-        <v>66</v>
-      </c>
-      <c r="I16" s="22" t="n">
-        <f aca="false">I6*前提!$E$33</f>
-        <v>66</v>
-      </c>
-      <c r="J16" s="22" t="n">
-        <f aca="false">J6*前提!$E$33</f>
-        <v>88</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <f aca="false">K6*前提!$E$33</f>
-        <v>88</v>
-      </c>
-      <c r="L16" s="22" t="n">
-        <f aca="false">L6*前提!$E$33</f>
-        <v>110</v>
-      </c>
-      <c r="M16" s="22" t="n">
-        <f aca="false">M6*前提!$E$33</f>
-        <v>110</v>
+      <c r="B16" s="31" t="n">
+        <f aca="false">$B$6*B15+$C$6*B14</f>
+        <v>35.4</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <f aca="false">$B$6*C15+$C$6*C14</f>
+        <v>44.4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B17" s="22" t="n">
-        <f aca="false">IF(B4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <f aca="false">IF(C4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <f aca="false">IF(D4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <f aca="false">IF(E4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <f aca="false">IF(F4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <f aca="false">IF(G4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="H17" s="22" t="n">
-        <f aca="false">IF(H4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="I17" s="22" t="n">
-        <f aca="false">IF(I4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="J17" s="22" t="n">
-        <f aca="false">IF(J4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <f aca="false">IF(K4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="L17" s="22" t="n">
-        <f aca="false">IF(L4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
-      </c>
-      <c r="M17" s="22" t="n">
-        <f aca="false">IF(M4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
-        <v>5</v>
+      <c r="B17" s="31" t="n">
+        <f aca="false">$B$7*B15+$C$7*B14</f>
+        <v>17.1</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <f aca="false">$B$7*C15+$C$7*C14</f>
+        <v>20.6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="23" t="n">
-        <f aca="false">SUM(B14:B17)</f>
-        <v>187</v>
-      </c>
-      <c r="C18" s="23" t="n">
-        <f aca="false">SUM(C14:C17)</f>
-        <v>446</v>
-      </c>
-      <c r="D18" s="23" t="n">
-        <f aca="false">SUM(D14:D17)</f>
-        <v>481.65</v>
-      </c>
-      <c r="E18" s="23" t="n">
-        <f aca="false">SUM(E14:E17)</f>
-        <v>213</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <f aca="false">SUM(F14:F17)</f>
-        <v>235</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <f aca="false">SUM(G14:G17)</f>
-        <v>235</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <f aca="false">SUM(H14:H17)</f>
-        <v>342</v>
-      </c>
-      <c r="I18" s="23" t="n">
-        <f aca="false">SUM(I14:I17)</f>
-        <v>342</v>
-      </c>
-      <c r="J18" s="23" t="n">
-        <f aca="false">SUM(J14:J17)</f>
-        <v>364</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <f aca="false">SUM(K14:K17)</f>
-        <v>364</v>
-      </c>
-      <c r="L18" s="23" t="n">
-        <f aca="false">SUM(L14:L17)</f>
-        <v>386</v>
-      </c>
-      <c r="M18" s="23" t="n">
-        <f aca="false">SUM(M14:M17)</f>
-        <v>386</v>
+      <c r="B18" s="31" t="n">
+        <f aca="false">$B$10*B15+$C$10*B14</f>
+        <v>9.9</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <f aca="false">$B$10*C15+$C$10*C14</f>
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <f aca="false">B16-B17</f>
+        <v>18.3</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <f aca="false">C16-C17</f>
+        <v>23.8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <f aca="false">B19/B16</f>
+        <v>0.516949152542373</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <f aca="false">C19/C16</f>
+        <v>0.536036036036036</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="23" t="n">
-        <f aca="false">B12-B18</f>
-        <v>613</v>
-      </c>
-      <c r="C20" s="23" t="n">
-        <f aca="false">C12-C18</f>
-        <v>1554</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <f aca="false">D12-D18</f>
-        <v>-481.65</v>
-      </c>
-      <c r="E20" s="23" t="n">
-        <f aca="false">E12-E18</f>
-        <v>-213</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <f aca="false">F12-F18</f>
-        <v>-187</v>
-      </c>
-      <c r="G20" s="23" t="n">
-        <f aca="false">G12-G18</f>
-        <v>-139</v>
-      </c>
-      <c r="H20" s="23" t="n">
-        <f aca="false">H12-H18</f>
-        <v>-246</v>
-      </c>
-      <c r="I20" s="23" t="n">
-        <f aca="false">I12-I18</f>
-        <v>-198</v>
-      </c>
-      <c r="J20" s="23" t="n">
-        <f aca="false">J12-J18</f>
-        <v>-220</v>
-      </c>
-      <c r="K20" s="23" t="n">
-        <f aca="false">K12-K18</f>
-        <v>-172</v>
-      </c>
-      <c r="L20" s="23" t="n">
-        <f aca="false">L12-L18</f>
-        <v>-194</v>
-      </c>
-      <c r="M20" s="23" t="n">
-        <f aca="false">M12-M18</f>
-        <v>-146</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="30" t="n">
-        <f aca="false">B20</f>
-        <v>613</v>
-      </c>
-      <c r="C21" s="30" t="n">
-        <f aca="false">B21+C20</f>
-        <v>2167</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <f aca="false">C21+D20</f>
-        <v>1685.35</v>
-      </c>
-      <c r="E21" s="30" t="n">
-        <f aca="false">D21+E20</f>
-        <v>1472.35</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <f aca="false">E21+F20</f>
-        <v>1285.35</v>
-      </c>
-      <c r="G21" s="30" t="n">
-        <f aca="false">F21+G20</f>
-        <v>1146.35</v>
-      </c>
-      <c r="H21" s="30" t="n">
-        <f aca="false">G21+H20</f>
-        <v>900.35</v>
-      </c>
-      <c r="I21" s="30" t="n">
-        <f aca="false">H21+I20</f>
-        <v>702.35</v>
-      </c>
-      <c r="J21" s="30" t="n">
-        <f aca="false">I21+J20</f>
-        <v>482.35</v>
-      </c>
-      <c r="K21" s="30" t="n">
-        <f aca="false">J21+K20</f>
-        <v>310.35</v>
-      </c>
-      <c r="L21" s="30" t="n">
-        <f aca="false">K21+L20</f>
-        <v>116.35</v>
-      </c>
-      <c r="M21" s="30" t="n">
-        <f aca="false">L21+M20</f>
-        <v>-29.6500000000001</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="25" t="n">
-        <f aca="false">MIN(B21:M21)</f>
-        <v>-29.6500000000001</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+      <c r="B25" s="24" t="n">
+        <f aca="false">SUM(B22:B24)</f>
+        <v>20</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <f aca="false">SUM(C22:C24)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="20" t="str">
-        <f aca="false">INDEX(B5:M5,MATCH(B23,B21:M21,0))</f>
-        <v>2027/9</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="26" t="n">
-        <f aca="false">SUM(B6:M6)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="B28" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B26" s="25" t="n">
-        <f aca="false">SUM(B7:M7)</f>
-        <v>1392</v>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B29" s="22" t="n">
+        <f aca="false">月次固定費!F6</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="22" t="n">
+        <f aca="false">月次固定費!F7</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="22" t="n">
+        <f aca="false">月次固定費!F22-月次固定費!F6-月次固定費!F7-SUM(月次固定費!F15:F17)</f>
+        <v>136</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="32" t="n">
+        <f aca="false">B19*B18-$B$29-B18/$B$28*$B$30</f>
+        <v>46.92</v>
+      </c>
+      <c r="C32" s="32" t="n">
+        <f aca="false">C19*C18-$B$29-C18/$B$28*$B$30</f>
+        <v>44.32</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="33" t="n">
+        <f aca="false">($B$31+B25)/B32</f>
+        <v>3.32480818414322</v>
+      </c>
+      <c r="C33" s="33" t="n">
+        <f aca="false">($B$31+C25)/C32</f>
+        <v>4.6028880866426</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" s="33" t="n">
+        <f aca="false">B33*B18/$B$28</f>
+        <v>4.11445012787724</v>
+      </c>
+      <c r="C34" s="33" t="n">
+        <f aca="false">C33*C18/$B$28</f>
+        <v>3.68231046931408</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="20" t="str">
+        <f aca="false">IF(B34&gt;B33,"制作ディレクター","営業")</f>
+        <v>制作ディレクター</v>
+      </c>
+      <c r="C35" s="20" t="str">
+        <f aca="false">IF(C34&gt;C33,"制作ディレクター","営業")</f>
+        <v>営業</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="31" t="n">
+        <f aca="false">B33*B18</f>
+        <v>32.9156010230179</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <f aca="false">C33*C18</f>
+        <v>29.4584837545126</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="32" t="n">
+        <f aca="false">B36*B16</f>
+        <v>1165.21227621483</v>
+      </c>
+      <c r="C37" s="32" t="n">
+        <f aca="false">C36*C16</f>
+        <v>1307.95667870036</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="26" t="n">
+        <f aca="false">1+B33+B34</f>
+        <v>8.43925831202046</v>
+      </c>
+      <c r="C38" s="26" t="n">
+        <f aca="false">1+C33+C34</f>
+        <v>9.28519855595668</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B36/3</f>
+        <v>10.9718670076726</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <f aca="false">C36/3</f>
+        <v>9.81949458483754</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -6771,170 +8557,808 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="22" t="n">
-        <f aca="false">初期費用!F17</f>
-        <v>886.65</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>154</v>
+      <c r="A4" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" s="34" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="22" t="n">
-        <f aca="false">月次固定費!F20</f>
-        <v>271</v>
-      </c>
-      <c r="C5" s="2"/>
+      <c r="A5" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="31" t="n">
-        <f aca="false">月次固定費!F23</f>
-        <v>10.4230769230769</v>
-      </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="22" t="n">
-        <f aca="false">前提!B14+前提!B15</f>
-        <v>2800</v>
-      </c>
-      <c r="C8" s="2"/>
+      <c r="A6" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="36" t="n">
+        <f aca="false">B6*前提!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="36" t="n">
+        <f aca="false">C6*前提!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <f aca="false">D6*前提!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <f aca="false">E6*前提!$B$21</f>
+        <v>48</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <f aca="false">F6*前提!$B$21</f>
+        <v>96</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <f aca="false">G6*前提!$B$21</f>
+        <v>96</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <f aca="false">H6*前提!$B$21</f>
+        <v>144</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <f aca="false">I6*前提!$B$21</f>
+        <v>144</v>
+      </c>
+      <c r="J7" s="36" t="n">
+        <f aca="false">J6*前提!$B$21</f>
+        <v>192</v>
+      </c>
+      <c r="K7" s="36" t="n">
+        <f aca="false">K6*前提!$B$21</f>
+        <v>192</v>
+      </c>
+      <c r="L7" s="36" t="n">
+        <f aca="false">L6*前提!$B$21</f>
+        <v>240</v>
+      </c>
+      <c r="M7" s="36" t="n">
+        <f aca="false">M6*前提!$B$21</f>
+        <v>240</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9" s="22" t="n">
-        <f aca="false">資金繰り!B23</f>
-        <v>-29.6500000000001</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>158</v>
+      <c r="A9" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <f aca="false">B7</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <f aca="false">C7</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <f aca="false">D7</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <f aca="false">E7</f>
+        <v>48</v>
+      </c>
+      <c r="G9" s="36" t="n">
+        <f aca="false">F7</f>
+        <v>96</v>
+      </c>
+      <c r="H9" s="36" t="n">
+        <f aca="false">G7</f>
+        <v>96</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <f aca="false">H7</f>
+        <v>144</v>
+      </c>
+      <c r="J9" s="36" t="n">
+        <f aca="false">I7</f>
+        <v>144</v>
+      </c>
+      <c r="K9" s="36" t="n">
+        <f aca="false">J7</f>
+        <v>192</v>
+      </c>
+      <c r="L9" s="36" t="n">
+        <f aca="false">K7</f>
+        <v>192</v>
+      </c>
+      <c r="M9" s="36" t="n">
+        <f aca="false">L7</f>
+        <v>240</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="6" t="str">
-        <f aca="false">資金繰り!B24</f>
+        <v>192</v>
+      </c>
+      <c r="B10" s="22" t="n">
+        <f aca="false">前提!$B$14</f>
+        <v>800</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="22" t="n">
+        <f aca="false">IF(B4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <f aca="false">IF(C4=前提!$B$16,前提!$B$15,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <f aca="false">IF(D4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <f aca="false">IF(E4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <f aca="false">IF(F4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <f aca="false">IF(G4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <f aca="false">IF(H4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <f aca="false">IF(I4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="22" t="n">
+        <f aca="false">IF(J4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <f aca="false">IF(K4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <f aca="false">IF(L4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <f aca="false">IF(M4=前提!$B$16,前提!$B$15,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="23" t="n">
+        <f aca="false">SUM(B9:B11)</f>
+        <v>800</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <f aca="false">SUM(C9:C11)</f>
+        <v>2000</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <f aca="false">SUM(D9:D11)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <f aca="false">SUM(E9:E11)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <f aca="false">SUM(F9:F11)</f>
+        <v>48</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <f aca="false">SUM(G9:G11)</f>
+        <v>96</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <f aca="false">SUM(H9:H11)</f>
+        <v>96</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <f aca="false">SUM(I9:I11)</f>
+        <v>144</v>
+      </c>
+      <c r="J12" s="23" t="n">
+        <f aca="false">SUM(J9:J11)</f>
+        <v>144</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <f aca="false">SUM(K9:K11)</f>
+        <v>192</v>
+      </c>
+      <c r="L12" s="23" t="n">
+        <f aca="false">SUM(L9:L11)</f>
+        <v>192</v>
+      </c>
+      <c r="M12" s="23" t="n">
+        <f aca="false">SUM(M9:M11)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,B4,初期費用!$F$5:$F$17)</f>
+        <v>131</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,C4,初期費用!$F$5:$F$17)</f>
+        <v>385</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,D4,初期費用!$F$5:$F$17)</f>
+        <v>370.65</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,E4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,F4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,G4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,H4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,I4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,J4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,K4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,L4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <f aca="false">SUMIF(初期費用!$B$5:$B$17,M4,初期費用!$F$5:$F$17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;B4,月次固定費!$F$5:$F$21)</f>
+        <v>61</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;C4,月次固定費!$F$5:$F$21)</f>
+        <v>61</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;D4,月次固定費!$F$5:$F$21)</f>
+        <v>111</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;E4,月次固定費!$F$5:$F$21)</f>
+        <v>191</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;F4,月次固定費!$F$5:$F$21)</f>
+        <v>191</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;G4,月次固定費!$F$5:$F$21)</f>
+        <v>191</v>
+      </c>
+      <c r="H15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;H4,月次固定費!$F$5:$F$21)</f>
+        <v>276</v>
+      </c>
+      <c r="I15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;I4,月次固定費!$F$5:$F$21)</f>
+        <v>276</v>
+      </c>
+      <c r="J15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;J4,月次固定費!$F$5:$F$21)</f>
+        <v>276</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;K4,月次固定費!$F$5:$F$21)</f>
+        <v>276</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;L4,月次固定費!$F$5:$F$21)</f>
+        <v>276</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <f aca="false">SUMIF(月次固定費!$B$5:$B$21,"&lt;="&amp;M4,月次固定費!$F$5:$F$21)</f>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="22" t="n">
+        <f aca="false">B6*前提!$E$33</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <f aca="false">C6*前提!$E$33</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <f aca="false">D6*前提!$E$33</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <f aca="false">E6*前提!$E$33</f>
+        <v>22</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <f aca="false">F6*前提!$E$33</f>
+        <v>44</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <f aca="false">G6*前提!$E$33</f>
+        <v>44</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <f aca="false">H6*前提!$E$33</f>
+        <v>66</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <f aca="false">I6*前提!$E$33</f>
+        <v>66</v>
+      </c>
+      <c r="J16" s="22" t="n">
+        <f aca="false">J6*前提!$E$33</f>
+        <v>88</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <f aca="false">K6*前提!$E$33</f>
+        <v>88</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <f aca="false">L6*前提!$E$33</f>
+        <v>110</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <f aca="false">M6*前提!$E$33</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="22" t="n">
+        <f aca="false">IF(B4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <f aca="false">IF(C4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <f aca="false">IF(D4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <f aca="false">IF(E4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <f aca="false">IF(F4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <f aca="false">IF(G4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <f aca="false">IF(H4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <f aca="false">IF(I4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="J17" s="22" t="n">
+        <f aca="false">IF(J4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <f aca="false">IF(K4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <f aca="false">IF(L4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <f aca="false">IF(M4&gt;=前提!$B$16,前提!$B$15*前提!$B$17/12,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="B18" s="23" t="n">
+        <f aca="false">SUM(B14:B17)</f>
+        <v>192</v>
+      </c>
+      <c r="C18" s="23" t="n">
+        <f aca="false">SUM(C14:C17)</f>
+        <v>451</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <f aca="false">SUM(D14:D17)</f>
+        <v>486.65</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <f aca="false">SUM(E14:E17)</f>
+        <v>218</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <f aca="false">SUM(F14:F17)</f>
+        <v>240</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <f aca="false">SUM(G14:G17)</f>
+        <v>240</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <f aca="false">SUM(H14:H17)</f>
+        <v>347</v>
+      </c>
+      <c r="I18" s="23" t="n">
+        <f aca="false">SUM(I14:I17)</f>
+        <v>347</v>
+      </c>
+      <c r="J18" s="23" t="n">
+        <f aca="false">SUM(J14:J17)</f>
+        <v>369</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <f aca="false">SUM(K14:K17)</f>
+        <v>369</v>
+      </c>
+      <c r="L18" s="23" t="n">
+        <f aca="false">SUM(L14:L17)</f>
+        <v>391</v>
+      </c>
+      <c r="M18" s="23" t="n">
+        <f aca="false">SUM(M14:M17)</f>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" s="23" t="n">
+        <f aca="false">B12-B18</f>
+        <v>608</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <f aca="false">C12-C18</f>
+        <v>1549</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <f aca="false">D12-D18</f>
+        <v>-486.65</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <f aca="false">E12-E18</f>
+        <v>-218</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <f aca="false">F12-F18</f>
+        <v>-192</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <f aca="false">G12-G18</f>
+        <v>-144</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <f aca="false">H12-H18</f>
+        <v>-251</v>
+      </c>
+      <c r="I20" s="23" t="n">
+        <f aca="false">I12-I18</f>
+        <v>-203</v>
+      </c>
+      <c r="J20" s="23" t="n">
+        <f aca="false">J12-J18</f>
+        <v>-225</v>
+      </c>
+      <c r="K20" s="23" t="n">
+        <f aca="false">K12-K18</f>
+        <v>-177</v>
+      </c>
+      <c r="L20" s="23" t="n">
+        <f aca="false">L12-L18</f>
+        <v>-199</v>
+      </c>
+      <c r="M20" s="23" t="n">
+        <f aca="false">M12-M18</f>
+        <v>-151</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="B21" s="37" t="n">
+        <f aca="false">B20</f>
+        <v>608</v>
+      </c>
+      <c r="C21" s="37" t="n">
+        <f aca="false">B21+C20</f>
+        <v>2157</v>
+      </c>
+      <c r="D21" s="37" t="n">
+        <f aca="false">C21+D20</f>
+        <v>1670.35</v>
+      </c>
+      <c r="E21" s="37" t="n">
+        <f aca="false">D21+E20</f>
+        <v>1452.35</v>
+      </c>
+      <c r="F21" s="37" t="n">
+        <f aca="false">E21+F20</f>
+        <v>1260.35</v>
+      </c>
+      <c r="G21" s="37" t="n">
+        <f aca="false">F21+G20</f>
+        <v>1116.35</v>
+      </c>
+      <c r="H21" s="37" t="n">
+        <f aca="false">G21+H20</f>
+        <v>865.35</v>
+      </c>
+      <c r="I21" s="37" t="n">
+        <f aca="false">H21+I20</f>
+        <v>662.35</v>
+      </c>
+      <c r="J21" s="37" t="n">
+        <f aca="false">I21+J20</f>
+        <v>437.35</v>
+      </c>
+      <c r="K21" s="37" t="n">
+        <f aca="false">J21+K20</f>
+        <v>260.35</v>
+      </c>
+      <c r="L21" s="37" t="n">
+        <f aca="false">K21+L20</f>
+        <v>61.3499999999999</v>
+      </c>
+      <c r="M21" s="37" t="n">
+        <f aca="false">L21+M20</f>
+        <v>-89.6500000000001</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="25" t="n">
+        <f aca="false">MIN(B21:M21)</f>
+        <v>-89.6500000000001</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="B24" s="20" t="str">
+        <f aca="false">INDEX(B5:M5,MATCH(B23,B21:M21,0))</f>
         <v>2027/9</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="22" t="n">
-        <f aca="false">資金繰り!M21</f>
-        <v>-29.6500000000001</v>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="22" t="n">
-        <f aca="false">月次固定費!F20*前提!B18</f>
-        <v>813</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="25" t="n">
-        <f aca="false">MAX(0,月次固定費!F20*前提!B18-資金繰り!B23)</f>
-        <v>842.65</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B15" s="32" t="n">
-        <f aca="false">B8+B14</f>
-        <v>3642.65</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>172</v>
+      <c r="A25" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="26" t="n">
+        <f aca="false">SUM(B6:M6)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <f aca="false">SUM(B7:M7)</f>
+        <v>1392</v>
       </c>
     </row>
   </sheetData>
@@ -6953,6 +9377,188 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="22" t="n">
+        <f aca="false">初期費用!F17</f>
+        <v>886.65</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="22" t="n">
+        <f aca="false">月次固定費!F22</f>
+        <v>276</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="38" t="n">
+        <f aca="false">月次固定費!F25</f>
+        <v>10.6153846153846</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="22" t="n">
+        <f aca="false">前提!B14+前提!B15</f>
+        <v>2800</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="22" t="n">
+        <f aca="false">資金繰り!B23</f>
+        <v>-89.6500000000001</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="6" t="str">
+        <f aca="false">資金繰り!B24</f>
+        <v>2027/9</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="22" t="n">
+        <f aca="false">資金繰り!M21</f>
+        <v>-89.6500000000001</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="22" t="n">
+        <f aca="false">月次固定費!F22*前提!B18</f>
+        <v>828</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <f aca="false">MAX(0,月次固定費!F22*前提!B18-資金繰り!B23)</f>
+        <v>917.65</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" s="39" t="n">
+        <f aca="false">B8+B14</f>
+        <v>3717.65</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6962,34 +9568,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>179</v>
+      <c r="B4" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>35</v>
@@ -7009,7 +9615,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>48</v>
@@ -7029,7 +9635,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>22</v>
@@ -7049,7 +9655,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>0</v>
@@ -7069,7 +9675,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>0.2</v>
@@ -7089,7 +9695,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>3</v>
@@ -7109,7 +9715,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>720</v>
@@ -7129,7 +9735,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>0.6</v>
@@ -7149,7 +9755,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1100</v>
@@ -7169,57 +9775,57 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B15" s="29" t="n">
+        <v>241</v>
+      </c>
+      <c r="B15" s="36" t="n">
         <f aca="false">B5*B6</f>
         <v>1680</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="36" t="n">
         <f aca="false">C5*C6</f>
         <v>9360</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="36" t="n">
         <f aca="false">D5*D6</f>
         <v>21280</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="36" t="n">
         <f aca="false">E5*E6</f>
         <v>37700</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="36" t="n">
         <f aca="false">F5*F6</f>
         <v>58900</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" s="29" t="n">
+        <v>242</v>
+      </c>
+      <c r="B16" s="36" t="n">
         <f aca="false">B8</f>
         <v>0</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="36" t="n">
         <f aca="false">C8</f>
         <v>0</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="36" t="n">
         <f aca="false">D8</f>
         <v>2000</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="36" t="n">
         <f aca="false">E8</f>
         <v>8000</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="36" t="n">
         <f aca="false">F8</f>
         <v>20000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">B15+B16</f>
@@ -7244,32 +9850,32 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="29" t="n">
+        <v>243</v>
+      </c>
+      <c r="B18" s="36" t="n">
         <f aca="false">B5*B7+B8*B9</f>
         <v>770</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="36" t="n">
         <f aca="false">C5*C7+C8*C9</f>
         <v>3960</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="36" t="n">
         <f aca="false">D5*D7+D8*D9</f>
         <v>8380</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="36" t="n">
         <f aca="false">E5*E7+E8*E9</f>
         <v>14600</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="36" t="n">
         <f aca="false">F5*F7+F8*F9</f>
         <v>22050</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="B19" s="23" t="n">
         <f aca="false">B17-B18</f>
@@ -7296,80 +9902,80 @@
       <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="34" t="n">
+      <c r="B20" s="41" t="n">
         <f aca="false">IF(B17=0,0,B19/B17)</f>
         <v>0.541666666666667</v>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C20" s="41" t="n">
         <f aca="false">IF(C17=0,0,C19/C17)</f>
         <v>0.576923076923077</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="41" t="n">
         <f aca="false">IF(D17=0,0,D19/D17)</f>
         <v>0.640034364261168</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E20" s="41" t="n">
         <f aca="false">IF(E17=0,0,E19/E17)</f>
         <v>0.680525164113786</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="41" t="n">
         <f aca="false">IF(F17=0,0,F19/F17)</f>
         <v>0.720532319391635</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B21" s="29" t="n">
+        <v>245</v>
+      </c>
+      <c r="B21" s="36" t="n">
         <f aca="false">B10*B11*B12</f>
         <v>1296</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="36" t="n">
         <f aca="false">C10*C11*C12</f>
         <v>4032</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="36" t="n">
         <f aca="false">D10*D11*D12</f>
         <v>8640</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="36" t="n">
         <f aca="false">E10*E11*E12</f>
         <v>14976</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="36" t="n">
         <f aca="false">F10*F11*F12</f>
         <v>23256</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B22" s="29" t="n">
+        <v>240</v>
+      </c>
+      <c r="B22" s="36" t="n">
         <f aca="false">B13</f>
         <v>1100</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="36" t="n">
         <f aca="false">C13</f>
         <v>1500</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="36" t="n">
         <f aca="false">D13</f>
         <v>3000</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="36" t="n">
         <f aca="false">E13</f>
         <v>5000</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="36" t="n">
         <f aca="false">F13</f>
         <v>12000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">B21+B22</f>
@@ -7394,7 +10000,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="B24" s="24" t="n">
         <f aca="false">B19-B23</f>
@@ -7419,92 +10025,92 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B25" s="34" t="n">
+        <v>248</v>
+      </c>
+      <c r="B25" s="41" t="n">
         <f aca="false">IF(B17=0,0,B24/B17)</f>
         <v>-0.88452380952381</v>
       </c>
-      <c r="C25" s="34" t="n">
+      <c r="C25" s="41" t="n">
         <f aca="false">IF(C17=0,0,C24/C17)</f>
         <v>-0.0141025641025641</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="41" t="n">
         <f aca="false">IF(D17=0,0,D24/D17)</f>
         <v>0.140034364261168</v>
       </c>
-      <c r="E25" s="34" t="n">
+      <c r="E25" s="41" t="n">
         <f aca="false">IF(E17=0,0,E24/E17)</f>
         <v>0.243413566739606</v>
       </c>
-      <c r="F25" s="34" t="n">
+      <c r="F25" s="41" t="n">
         <f aca="false">IF(F17=0,0,F24/F17)</f>
         <v>0.273688212927757</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B27" s="35" t="n">
+        <v>249</v>
+      </c>
+      <c r="B27" s="42" t="n">
         <f aca="false">IF(B17=0,0,B16/B17)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="35" t="n">
+      <c r="C27" s="42" t="n">
         <f aca="false">IF(C17=0,0,C16/C17)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="35" t="n">
+      <c r="D27" s="42" t="n">
         <f aca="false">IF(D17=0,0,D16/D17)</f>
         <v>0.0859106529209622</v>
       </c>
-      <c r="E27" s="35" t="n">
+      <c r="E27" s="42" t="n">
         <f aca="false">IF(E17=0,0,E16/E17)</f>
         <v>0.175054704595186</v>
       </c>
-      <c r="F27" s="35" t="n">
+      <c r="F27" s="42" t="n">
         <f aca="false">IF(F17=0,0,F16/F17)</f>
         <v>0.253485424588086</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="B28" s="29" t="n">
+        <v>250</v>
+      </c>
+      <c r="B28" s="36" t="n">
         <f aca="false">IF(B10=0,0,B17/B10)</f>
         <v>560</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="36" t="n">
         <f aca="false">IF(C10=0,0,C17/C10)</f>
         <v>1170</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="36" t="n">
         <f aca="false">IF(D10=0,0,D17/D10)</f>
         <v>1455</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="36" t="n">
         <f aca="false">IF(E10=0,0,E17/E10)</f>
         <v>1757.69230769231</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="36" t="n">
         <f aca="false">IF(F10=0,0,F17/F10)</f>
         <v>2076.31578947368</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
